--- a/data/stx_xlsx/WTWa.ST.xlsx
+++ b/data/stx_xlsx/WTWa.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="285">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -507,25 +507,28 @@
     <t>Total Equity</t>
   </si>
   <si>
+    <t>Borrowings (Do not use)</t>
+  </si>
+  <si>
+    <t>Non-current lease liabilities</t>
+  </si>
+  <si>
+    <t>Deferred tax liabilities</t>
+  </si>
+  <si>
+    <t>Other Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Other provisions</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Liabilities</t>
+  </si>
+  <si>
+    <t>Total Non-Current Liabilities</t>
+  </si>
+  <si>
     <t>Borrowings</t>
-  </si>
-  <si>
-    <t>Non-current lease liabilities</t>
-  </si>
-  <si>
-    <t>Deferred tax liabilities</t>
-  </si>
-  <si>
-    <t>Other Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>Other provisions</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Liabilities</t>
-  </si>
-  <si>
-    <t>Total Non-Current Liabilities</t>
   </si>
   <si>
     <t>Current lease liabilities</t>
@@ -1019,7 +1022,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1101,6 +1104,9 @@
     </xf>
     <xf borderId="5" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -5007,7 +5013,7 @@
       <c r="G53" s="21"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="28" t="s">
         <v>162</v>
       </c>
       <c r="B54" s="17">
@@ -5137,7 +5143,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="16" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B61" s="23">
         <v>5.25</v>
@@ -5156,7 +5162,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B62" s="23">
         <v>39.04</v>
@@ -5175,7 +5181,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B63" s="23">
         <v>67.25</v>
@@ -5194,7 +5200,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B64" s="23">
         <v>8.64</v>
@@ -5213,7 +5219,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B65" s="18">
         <v>0.0</v>
@@ -5230,7 +5236,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B66" s="23">
         <v>29.41</v>
@@ -5249,7 +5255,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B67" s="23">
         <v>65.39</v>
@@ -5268,7 +5274,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -5279,7 +5285,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -5305,7 +5311,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="19">
@@ -5320,7 +5326,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B72" s="21">
         <v>219.35</v>
@@ -5339,7 +5345,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B73" s="21">
         <v>580.52</v>
@@ -5358,7 +5364,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -5371,7 +5377,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B75" s="21">
         <v>1396.36</v>
@@ -5390,7 +5396,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B76" s="23">
         <v>13.71</v>
@@ -5409,7 +5415,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B77" s="23">
         <v>13.38</v>
@@ -5428,7 +5434,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B78" s="23">
         <v>0.33</v>
@@ -5447,7 +5453,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B79" s="18"/>
       <c r="C79" s="23">
@@ -5464,7 +5470,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B80" s="18"/>
       <c r="C80" s="23">
@@ -5481,7 +5487,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B81" s="18"/>
       <c r="C81" s="23">
@@ -5498,7 +5504,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B82" s="18"/>
       <c r="C82" s="23">
@@ -5515,7 +5521,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B83" s="18"/>
       <c r="C83" s="17">
@@ -5532,7 +5538,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="23">
@@ -5549,7 +5555,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="23">
@@ -5566,7 +5572,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B86" s="18"/>
       <c r="C86" s="17">
@@ -5583,7 +5589,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B87" s="18"/>
       <c r="C87" s="23">
@@ -5600,7 +5606,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B88" s="18"/>
       <c r="C88" s="17">
@@ -5617,7 +5623,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="18"/>
       <c r="C89" s="17">
@@ -5632,7 +5638,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="18"/>
       <c r="C90" s="18"/>
@@ -5643,7 +5649,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
@@ -5654,7 +5660,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
@@ -5665,7 +5671,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B93" s="23">
         <v>2.0</v>
@@ -5684,7 +5690,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B94" s="23">
         <v>0.15</v>
@@ -5703,7 +5709,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B95" s="23">
         <v>2.0</v>
@@ -5722,7 +5728,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
@@ -5737,7 +5743,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B97" s="23">
         <v>0.85</v>
@@ -5754,7 +5760,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B98" s="23">
         <v>11.71</v>
@@ -5773,7 +5779,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B99" s="23">
         <v>11.38</v>
@@ -5792,7 +5798,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B100" s="23">
         <v>0.33</v>
@@ -5811,7 +5817,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B101" s="17">
         <v>427.0</v>
@@ -6752,7 +6758,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6914,16 +6920,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -6949,7 +6955,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -6998,7 +7004,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B21" s="17">
         <v>330.99</v>
@@ -7017,7 +7023,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B22" s="23">
         <v>1.06</v>
@@ -7036,7 +7042,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" s="19">
         <v>-13.35</v>
@@ -7055,7 +7061,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" s="19">
         <v>-16.31</v>
@@ -7074,7 +7080,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B25" s="23">
         <v>36.65</v>
@@ -7093,7 +7099,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B26" s="23">
         <v>3.39</v>
@@ -7112,7 +7118,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B27" s="23">
         <v>36.12</v>
@@ -7131,7 +7137,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B28" s="18">
         <v>0.0</v>
@@ -7150,7 +7156,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B29" s="23">
         <v>7.84</v>
@@ -7169,7 +7175,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" s="19">
         <v>-17.69</v>
@@ -7188,7 +7194,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B31" s="23">
         <v>0.11</v>
@@ -7205,7 +7211,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B32" s="24">
         <v>66.3</v>
@@ -7224,7 +7230,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B33" s="19">
         <v>-9.96</v>
@@ -7239,7 +7245,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -7254,7 +7260,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B35" s="23">
         <v>8.16</v>
@@ -7273,7 +7279,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B36" s="19">
         <v>-23.73</v>
@@ -7292,7 +7298,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B37" s="19">
         <v>-0.32</v>
@@ -7311,7 +7317,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B38" s="19">
         <v>-1.8</v>
@@ -7324,7 +7330,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="23">
@@ -7339,7 +7345,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -7350,7 +7356,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -7363,7 +7369,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B42" s="26">
         <v>-27.64</v>
@@ -7382,7 +7388,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -7393,7 +7399,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -7404,7 +7410,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18"/>
@@ -7415,7 +7421,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B46" s="23">
         <v>2.33</v>
@@ -7434,7 +7440,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -7445,7 +7451,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18"/>
@@ -7460,7 +7466,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -7475,7 +7481,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -7490,7 +7496,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -7501,7 +7507,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -7512,7 +7518,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -7523,7 +7529,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
@@ -7534,7 +7540,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B55" s="23">
         <v>24.78</v>
@@ -7553,7 +7559,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B56" s="19">
         <v>-22.67</v>
@@ -7572,7 +7578,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B57" s="19">
         <v>-43.96</v>
@@ -7591,7 +7597,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B58" s="19">
         <v>-6.14</v>
@@ -7606,7 +7612,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
@@ -7617,7 +7623,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B60" s="19">
         <v>-14.3</v>
@@ -7634,7 +7640,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="23">
@@ -7649,7 +7655,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B62" s="26">
         <v>-59.95</v>
@@ -7668,7 +7674,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B63" s="17">
         <v>111.21</v>
@@ -7687,7 +7693,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B64" s="23">
         <v>89.12</v>
@@ -7706,7 +7712,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B65" s="19">
         <v>-0.11</v>
@@ -7725,7 +7731,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B66" s="23">
         <v>0.11</v>
@@ -7738,7 +7744,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B67" s="26">
         <v>-21.29</v>
@@ -8713,7 +8719,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8913,7 +8919,7 @@
     </row>
     <row r="18">
       <c r="A18" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -8942,408 +8948,408 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
+      <c r="A20" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="31">
+      <c r="A21" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="32">
         <v>1047.01</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>1294.19</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+      <c r="A22" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B23" s="31">
+      <c r="A23" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="32">
         <v>855.17</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="32">
         <v>1157.38</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="31">
+      <c r="D23" s="33"/>
+      <c r="E23" s="32">
         <v>980.98</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
+      <c r="A24" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="B25" s="33">
+      <c r="A25" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" s="34">
         <v>61.89</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>83.76</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33">
+      <c r="D25" s="33"/>
+      <c r="E25" s="34">
         <v>93.73</v>
       </c>
-      <c r="F25" s="32"/>
+      <c r="F25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
+      <c r="A26" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="B27" s="34">
+      <c r="A27" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="B27" s="35">
         <v>10.9</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>3.27</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
+      <c r="A28" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="B29" s="34">
+      <c r="A29" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" s="35">
         <v>1.16</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="35">
         <v>0.84</v>
       </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34">
+      <c r="D29" s="35"/>
+      <c r="E29" s="35">
         <v>0.0</v>
       </c>
-      <c r="F29" s="34"/>
+      <c r="F29" s="35"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B30" s="34">
+      <c r="A30" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="B30" s="35">
         <v>1.66</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>1.2</v>
       </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34">
+      <c r="D30" s="35"/>
+      <c r="E30" s="35">
         <v>0.0</v>
       </c>
-      <c r="F30" s="34"/>
+      <c r="F30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
+      <c r="A31" s="29" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" s="33">
+      <c r="A32" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="B32" s="34">
         <v>0.77</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="34">
         <v>1.07</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
+      <c r="A33" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B34" s="34">
         <v>0.9</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>1.19</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
+      <c r="A35" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B36" s="34">
         <v>9.18</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>30.59</v>
       </c>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="A37" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="B38" s="34">
         <v>9.54</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>13.74</v>
       </c>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
+      <c r="A39" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="33">
+      <c r="A40" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" s="34">
         <v>59.64</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="34">
         <v>66.16</v>
       </c>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
+      <c r="A41" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="B42" s="32">
         <v>171.46</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>52.2</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
+      <c r="A43" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B44" s="35">
+      <c r="A44" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="B44" s="36">
         <v>-3.02</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
+      <c r="A45" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>277</v>
-      </c>
-      <c r="B46" s="33">
+      <c r="A46" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="B46" s="34">
         <v>1.11</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="34">
         <v>1.34</v>
       </c>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+      <c r="A47" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B48" s="33">
+      <c r="A48" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="B48" s="34">
         <v>10.5</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>11.48</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
+      <c r="A49" s="29" t="s">
+        <v>281</v>
+      </c>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B50" s="34">
         <v>9.98</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>25.36</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
+      <c r="A51" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="B52" s="33">
+      <c r="A52" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="B52" s="34">
         <v>11.35</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="34">
         <v>34.56</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
     </row>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1"/>
